--- a/output/laminas_provinciales/prov_i_peringr_median_a_2024_aysen.xlsx
+++ b/output/laminas_provinciales/prov_i_peringr_median_a_2024_aysen.xlsx
@@ -74,7 +74,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-07 11:14</t>
+    <t xml:space="preserve">2026-09-09 22:14</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/laminas_provinciales/prov_i_peringr_median_a_2024_aysen.xlsx
+++ b/output/laminas_provinciales/prov_i_peringr_median_a_2024_aysen.xlsx
@@ -74,7 +74,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 22:14</t>
+    <t xml:space="preserve">2026-09-17 13:41</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -955,26 +955,26 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="B2" s="2" t="n">
-        <v>9.82</v>
+        <v>9.76</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="B3" s="2" t="n">
-        <v>11.26</v>
+        <v>9.82</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="B4" s="2" t="n">
-        <v>9.76</v>
+        <v>11.26</v>
       </c>
     </row>
     <row r="5">
@@ -1015,101 +1015,101 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>31</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>10.77</v>
+        <v>10.83</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>32</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>10.2</v>
+        <v>10.46</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>28</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>9.82</v>
+        <v>9.76</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>31</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>11.83</v>
+        <v>10.77</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>32</v>
       </c>
       <c r="C6" s="2" t="n">
-        <v>11.08</v>
+        <v>10.2</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>28</v>
       </c>
       <c r="C7" s="2" t="n">
-        <v>11.26</v>
+        <v>9.82</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>31</v>
       </c>
       <c r="C8" s="2" t="n">
-        <v>10.83</v>
+        <v>11.83</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="s">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>32</v>
       </c>
       <c r="C9" s="2" t="n">
-        <v>10.46</v>
+        <v>11.08</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="s">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>28</v>
       </c>
       <c r="C10" s="2" t="n">
-        <v>9.76</v>
+        <v>11.26</v>
       </c>
     </row>
     <row r="11">

--- a/output/laminas_provinciales/prov_i_peringr_median_a_2024_aysen.xlsx
+++ b/output/laminas_provinciales/prov_i_peringr_median_a_2024_aysen.xlsx
@@ -74,7 +74,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-17 13:41</t>
+    <t xml:space="preserve">2026-09-25 21:36</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -530,7 +530,7 @@
         <v>-0.65</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>-5.23</v>
+        <v>-5.26</v>
       </c>
       <c r="G2" s="2" t="n">
         <v>5</v>
@@ -573,10 +573,10 @@
         <v>10.46</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>-0.7</v>
+        <v>-0.71</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>-6.69</v>
+        <v>-6.76</v>
       </c>
       <c r="G4" s="2" t="n">
         <v>5</v>
@@ -622,7 +622,7 @@
         <v>-0.41</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>-4.93</v>
+        <v>-4.95</v>
       </c>
       <c r="G6" s="2" t="n">
         <v>4</v>
@@ -665,10 +665,10 @@
         <v>12.42</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>-0.47</v>
+        <v>-0.48</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>-3.78</v>
+        <v>-3.84</v>
       </c>
       <c r="G8" s="2" t="n">
         <v>3</v>
@@ -691,7 +691,7 @@
         <v>-0.52</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>-6.13</v>
+        <v>-6.14</v>
       </c>
       <c r="G9" s="2" t="n">
         <v>3</v>
@@ -714,7 +714,7 @@
         <v>-0.53</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>-5.11</v>
+        <v>-5.09</v>
       </c>
       <c r="G10" s="2" t="n">
         <v>3</v>
@@ -737,7 +737,7 @@
         <v>0.08</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="G11" s="2" t="n">
         <v>2</v>
@@ -760,7 +760,7 @@
         <v>-0.07</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>-0.77</v>
+        <v>-0.8</v>
       </c>
       <c r="G12" s="2" t="n">
         <v>2</v>
@@ -783,7 +783,7 @@
         <v>-0.04</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>-0.4</v>
+        <v>-0.35</v>
       </c>
       <c r="G13" s="2" t="n">
         <v>2</v>
@@ -803,10 +803,10 @@
         <v>12.63</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>2.77</v>
+        <v>2.82</v>
       </c>
       <c r="G14" s="2" t="n">
         <v>1</v>
@@ -829,7 +829,7 @@
         <v>0.02</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>0.21</v>
+        <v>0.25</v>
       </c>
       <c r="G15" s="2" t="n">
         <v>1</v>

--- a/output/laminas_provinciales/prov_i_peringr_median_a_2024_aysen.xlsx
+++ b/output/laminas_provinciales/prov_i_peringr_median_a_2024_aysen.xlsx
@@ -55,7 +55,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-28 21:40</t>
+    <t xml:space="preserve">2026-10-05 07:08</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
